--- a/artfynd/A 22238-2024 artfynd.xlsx
+++ b/artfynd/A 22238-2024 artfynd.xlsx
@@ -813,12 +813,7 @@
         <v>74437711</v>
       </c>
       <c r="B3" t="n">
-        <v>103415</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -854,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468892.7224517969</v>
+        <v>468893</v>
       </c>
       <c r="R3" t="n">
-        <v>6292308.081234087</v>
+        <v>6292308</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,19 +882,9 @@
           <t>2002-09-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2002-09-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 22238-2024 artfynd.xlsx
+++ b/artfynd/A 22238-2024 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74437711</v>
       </c>
       <c r="B3" t="n">
-        <v>105794</v>
+        <v>105803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22238-2024 artfynd.xlsx
+++ b/artfynd/A 22238-2024 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74437711</v>
       </c>
       <c r="B3" t="n">
-        <v>105803</v>
+        <v>105808</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22238-2024 artfynd.xlsx
+++ b/artfynd/A 22238-2024 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74437711</v>
       </c>
       <c r="B3" t="n">
-        <v>105808</v>
+        <v>105836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22238-2024 artfynd.xlsx
+++ b/artfynd/A 22238-2024 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74437711</v>
       </c>
       <c r="B3" t="n">
-        <v>105836</v>
+        <v>105842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22238-2024 artfynd.xlsx
+++ b/artfynd/A 22238-2024 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74437711</v>
       </c>
       <c r="B3" t="n">
-        <v>105842</v>
+        <v>105849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22238-2024 artfynd.xlsx
+++ b/artfynd/A 22238-2024 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74437711</v>
       </c>
       <c r="B3" t="n">
-        <v>105849</v>
+        <v>105853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22238-2024 artfynd.xlsx
+++ b/artfynd/A 22238-2024 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74437711</v>
       </c>
       <c r="B3" t="n">
-        <v>105853</v>
+        <v>105860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22238-2024 artfynd.xlsx
+++ b/artfynd/A 22238-2024 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74437711</v>
       </c>
       <c r="B3" t="n">
-        <v>105863</v>
+        <v>105868</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22238-2024 artfynd.xlsx
+++ b/artfynd/A 22238-2024 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74437711</v>
       </c>
       <c r="B3" t="n">
-        <v>105868</v>
+        <v>105876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22238-2024 artfynd.xlsx
+++ b/artfynd/A 22238-2024 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>74437711</v>
       </c>
       <c r="B3" t="n">
-        <v>105876</v>
+        <v>105886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22238-2024 artfynd.xlsx
+++ b/artfynd/A 22238-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>621347</v>
       </c>
       <c r="B2" t="n">
-        <v>103415</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468901.604260034</v>
+        <v>468902</v>
       </c>
       <c r="R2" t="n">
-        <v>6292321.165511137</v>
+        <v>6292321</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2006-09-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2006-09-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -813,7 +798,7 @@
         <v>74437711</v>
       </c>
       <c r="B3" t="n">
-        <v>105886</v>
+        <v>106400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22238-2024 artfynd.xlsx
+++ b/artfynd/A 22238-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/621347</t>
         </is>
       </c>
     </row>
@@ -908,8 +918,17 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74437711</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>